--- a/MS.xlsx
+++ b/MS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DinhNguyen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UpdateCode\Microservice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859F5BEA-7D78-496B-AE7F-3B57BB5D78E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED002983-04BB-4215-BD2F-43734B27650B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{E4E67C5F-CECD-47C9-80EC-165B2C750E5D}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Register" sheetId="3" r:id="rId2"/>
     <sheet name="Login" sheetId="1" r:id="rId3"/>
     <sheet name="Access_Request" sheetId="4" r:id="rId4"/>
+    <sheet name="Zull and Kafka" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -97,15 +98,15 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>597790</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>113119</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD64C87A-B0C4-31C1-0FF3-29FAD2FD6479}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5B05D27-8337-8A80-0FD5-1A322FE6DD46}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -122,7 +123,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="18276190" cy="9447619"/>
+          <a:ext cx="18276190" cy="9600000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -314,6 +315,187 @@
         <a:xfrm>
           <a:off x="0" y="7048500"/>
           <a:ext cx="14866667" cy="6914286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>264914</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>179690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF1A8652-3116-8F51-3440-6D5DD6EF114A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14478000"/>
+          <a:ext cx="14285714" cy="10276190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>597790</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>160881</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE43A58C-C8CA-600F-6323-C409B4B4FAFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18276190" cy="8352381"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>597790</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>113480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BAB6271-C62C-76C9-1B97-A814E4049E19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8601075"/>
+          <a:ext cx="18276190" cy="6561905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>265448</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>28000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B68E4FD6-B6A7-ADF4-1924-028E45E299C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="15430500"/>
+          <a:ext cx="10019048" cy="4600000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -658,4 +840,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F7F5C3-914A-4C84-AFAF-6C0A58E8C563}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>